--- a/StockFlowAI/config/parametres.xlsx
+++ b/StockFlowAI/config/parametres.xlsx
@@ -436,7 +436,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"TEXTILE_HOMME": ["S", "M", "L"], "TEXTILE_FEMME": ["36", "38", "40"], "DEFAUT": ["S", "M", "L"]}</t>
+          <t>{"TEXTILE_HOMME": ["S", "M", "L"], "TEXTILE_FEMME": ["36", "38", "40"], "LETTRE": ["S", "M", "L"], "CHAUSSURE": ["42", "43", "44"], "ENFANT": [], "AUTRE": [], "DEFAUT": ["S", "M", "L"]}</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -824,7 +824,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DEFAUT</t>
+          <t>LETTRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DEFAUT</t>
+          <t>LETTRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -848,10 +848,82 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>LETTRE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CHAUSSURE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CHAUSSURE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CHAUSSURE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>DEFAUT</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DEFAUT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DEFAUT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>L</t>
         </is>

--- a/StockFlowAI/config/parametres.xlsx
+++ b/StockFlowAI/config/parametres.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,30 +696,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>top_n_references</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>30</v>
+          <t>magasins_exclus_flux</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>["CENTRAL"]</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>max_iterations</t>
+          <t>top_n_references</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5000</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>max_iterations</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>quantite_min_transfert</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B30" t="n">
         <v>1</v>
       </c>
     </row>

--- a/StockFlowAI/config/parametres.xlsx
+++ b/StockFlowAI/config/parametres.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["PRESTA", "NAPLES"]</t>
         </is>
       </c>
     </row>
